--- a/kospi200.xlsx
+++ b/kospi200.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>183,600</t>
+          <t>180,100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>하락5,400</t>
+          <t>하락8,900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8,982,083</t>
+          <t>32,036,851</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,656,713</t>
+          <t>5,834,939</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10,868,455</t>
+          <t>10,661,268</t>
         </is>
       </c>
     </row>
@@ -498,32 +498,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>958,000</t>
+          <t>933,000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>하락37,000</t>
+          <t>하락62,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-6.23%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1,186,786</t>
+          <t>4,637,355</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,142,800</t>
+          <t>4,391,534</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6,827,689</t>
+          <t>6,649,513</t>
         </is>
       </c>
     </row>
@@ -535,32 +535,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>495,500</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>하락5,500</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>234,254</t>
+          <t>954,312</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115,961</t>
+          <t>469,080</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,014,575</t>
+          <t>1,003,313</t>
         </is>
       </c>
     </row>
@@ -572,32 +572,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>384,500</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>하락7,000</t>
+          <t>하락9,500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>64,074</t>
+          <t>274,036</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24,997</t>
+          <t>105,845</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>905,580</t>
+          <t>899,730</t>
         </is>
       </c>
     </row>
@@ -609,32 +609,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>574,500</t>
+          <t>558,000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>하락30,500</t>
+          <t>하락47,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-5.04%</t>
+          <t>-7.77%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>154,610</t>
+          <t>600,617</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>89,870</t>
+          <t>342,127</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>758,840</t>
+          <t>737,046</t>
         </is>
       </c>
     </row>
@@ -646,32 +646,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1,596,000</t>
+          <t>1,585,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>상승11,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7,124</t>
+          <t>30,266</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11,412</t>
+          <t>48,241</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>738,804</t>
+          <t>733,712</t>
         </is>
       </c>
     </row>
@@ -683,32 +683,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1,405,000</t>
+          <t>1,369,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>하락31,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46,062</t>
+          <t>158,093</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>64,874</t>
+          <t>219,679</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>724,466</t>
+          <t>705,903</t>
         </is>
       </c>
     </row>
@@ -720,32 +720,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>102,300</t>
+          <t>100,900</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>690,300</t>
+          <t>2,606,562</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70,798</t>
+          <t>264,427</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>655,294</t>
+          <t>646,326</t>
         </is>
       </c>
     </row>
@@ -757,32 +757,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>156,500</t>
+          <t>154,700</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>하락3,200</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>233,479</t>
+          <t>836,058</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36,381</t>
+          <t>129,985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>610,996</t>
+          <t>603,969</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>152,100</t>
+          <t>152,200</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>상승2,700</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>266,126</t>
+          <t>1,058,520</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40,245</t>
+          <t>160,852</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>567,106</t>
+          <t>567,478</t>
         </is>
       </c>
     </row>
@@ -831,32 +831,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>523,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락12,000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>49,039</t>
+          <t>179,100</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25,638</t>
+          <t>92,595</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>548,947</t>
+          <t>536,352</t>
         </is>
       </c>
     </row>
@@ -868,32 +868,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>286,500</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80,269</t>
+          <t>357,312</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23,092</t>
+          <t>100,125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>486,983</t>
+          <t>472,535</t>
         </is>
       </c>
     </row>
@@ -905,32 +905,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>205,000</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>121,618</t>
+          <t>441,074</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>89,929</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>473,649</t>
+          <t>469,028</t>
         </is>
       </c>
     </row>
@@ -942,32 +942,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>222,000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44,046</t>
+          <t>381,148</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9,969</t>
+          <t>85,525</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>444,000</t>
         </is>
       </c>
     </row>
@@ -979,32 +979,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>93,600</t>
+          <t>93,400</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>상승1,300</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>206,724</t>
+          <t>1,065,634</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19,276</t>
+          <t>99,684</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>444,276</t>
+          <t>443,327</t>
         </is>
       </c>
     </row>
@@ -1016,32 +1016,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>128,400</t>
+          <t>125,700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>상승3,700</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>397,409</t>
+          <t>932,262</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51,087</t>
+          <t>118,594</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>393,435</t>
+          <t>385,162</t>
         </is>
       </c>
     </row>
@@ -1053,32 +1053,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>68,100</t>
+          <t>65,300</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>상승800</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1,585,798</t>
+          <t>3,636,252</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>107,475</t>
+          <t>243,863</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>378,170</t>
+          <t>362,622</t>
         </is>
       </c>
     </row>
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>399,000</t>
+          <t>398,500</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락3,500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47,328</t>
+          <t>198,820</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18,836</t>
+          <t>79,160</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>362,023</t>
+          <t>361,569</t>
         </is>
       </c>
     </row>
@@ -1127,32 +1127,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>982,000</t>
+          <t>965,000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>하락10,000</t>
+          <t>하락27,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24,843</t>
+          <t>82,589</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24,593</t>
+          <t>80,704</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>353,983</t>
+          <t>347,855</t>
         </is>
       </c>
     </row>
@@ -1164,32 +1164,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>459,000</t>
+          <t>457,000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>상승4,500</t>
+          <t>상승2,500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>180,350</t>
+          <t>486,526</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>82,796</t>
+          <t>222,335</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>342,844</t>
+          <t>341,350</t>
         </is>
       </c>
     </row>
@@ -1201,106 +1201,106 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>215,500</t>
+          <t>211,500</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>91,601</t>
+          <t>414,759</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19,779</t>
+          <t>88,578</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>338,017</t>
+          <t>331,743</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>407,500</t>
+          <t>1,546,000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>상승3,500</t>
+          <t>하락47,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>145,272</t>
+          <t>16,077</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>59,210</t>
+          <t>24,912</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>328,386</t>
+          <t>322,696</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1,570,000</t>
+          <t>396,500</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>하락23,000</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3,420</t>
+          <t>455,849</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5,379</t>
+          <t>183,218</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>327,706</t>
+          <t>319,522</t>
         </is>
       </c>
     </row>
@@ -1312,32 +1312,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>108,800</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166,260</t>
+          <t>781,449</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18,138</t>
+          <t>85,336</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>303,375</t>
+          <t>302,818</t>
         </is>
       </c>
     </row>
@@ -1349,32 +1349,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46,200</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>442,634</t>
+          <t>1,498,854</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20,393</t>
+          <t>69,021</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>296,587</t>
+          <t>295,303</t>
         </is>
       </c>
     </row>
@@ -1386,217 +1386,217 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>348,500</t>
+          <t>342,500</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>상승6,500</t>
+          <t>상승500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>91,295</t>
+          <t>258,671</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31,740</t>
+          <t>89,275</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>282,051</t>
+          <t>277,195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>2,860,000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락130,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-2.00%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>133,735</t>
+          <t>43,757</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39,311</t>
+          <t>127,499</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>280,218</t>
+          <t>266,682</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2,920,000</t>
+          <t>375,000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>하락70,000</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13,624</t>
+          <t>171,510</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>40,647</t>
+          <t>65,114</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>272,277</t>
+          <t>265,399</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>381,500</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>하락22,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-7.33%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48,593</t>
+          <t>650,100</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18,704</t>
+          <t>186,453</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>269,999</t>
+          <t>264,968</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>135,100</t>
+          <t>834,000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>341,165</t>
+          <t>94,565</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>46,110</t>
+          <t>79,627</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>255,230</t>
+          <t>250,200</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LS ELECTRIC</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>848,000</t>
+          <t>129,700</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>하락6,900</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22,191</t>
+          <t>872,669</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18,880</t>
+          <t>116,209</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>254,400</t>
+          <t>245,028</t>
         </is>
       </c>
     </row>
@@ -1608,32 +1608,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>348,500</t>
+          <t>336,500</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락9,500</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33,547</t>
+          <t>175,762</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11,676</t>
+          <t>60,287</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>252,672</t>
+          <t>243,972</t>
         </is>
       </c>
     </row>
@@ -1645,32 +1645,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33,050</t>
+          <t>33,200</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>상승200</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>190,474</t>
+          <t>1,582,887</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6,289</t>
+          <t>52,639</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>242,612</t>
+          <t>243,713</t>
         </is>
       </c>
     </row>
@@ -1682,32 +1682,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>26,950</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>931,754</t>
+          <t>2,633,712</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25,324</t>
+          <t>70,581</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>237,160</t>
+          <t>231,880</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1719,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>314,000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>상승2,000</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>50,436</t>
+          <t>213,144</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16,177</t>
+          <t>67,583</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>225,895</t>
+          <t>221,660</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>49,400</t>
+          <t>48,650</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>상승350</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>269,309</t>
+          <t>1,231,106</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13,273</t>
+          <t>60,295</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>218,727</t>
+          <t>215,406</t>
         </is>
       </c>
     </row>
@@ -1793,32 +1793,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>271,500</t>
+          <t>266,500</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>상승6,500</t>
+          <t>상승1,500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28,611</t>
+          <t>118,098</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7,692</t>
+          <t>31,736</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>214,466</t>
+          <t>210,517</t>
         </is>
       </c>
     </row>
@@ -1830,32 +1830,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>461,000</t>
+          <t>453,000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>하락29,000</t>
+          <t>하락37,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-5.92%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29,812</t>
+          <t>123,567</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13,933</t>
+          <t>56,664</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>212,111</t>
+          <t>208,431</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>191,600</t>
+          <t>189,800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>상승900</t>
+          <t>하락900</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>215,674</t>
+          <t>644,522</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41,276</t>
+          <t>123,436</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>209,117</t>
+          <t>207,152</t>
         </is>
       </c>
     </row>
@@ -1904,32 +1904,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1,247,000</t>
+          <t>1,239,000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락11,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13,526</t>
+          <t>50,777</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>16,882</t>
+          <t>63,101</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>201,937</t>
+          <t>200,642</t>
         </is>
       </c>
     </row>
@@ -1941,32 +1941,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>115,100</t>
+          <t>114,200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>상승3,700</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>+3.32%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>63,194</t>
+          <t>339,679</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7,211</t>
+          <t>39,169</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>194,520</t>
+          <t>192,999</t>
         </is>
       </c>
     </row>
@@ -1978,106 +1978,106 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>111,900</t>
+          <t>111,300</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>하락2,200</t>
+          <t>하락2,800</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>67,498</t>
+          <t>300,798</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7,593</t>
+          <t>33,711</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>189,170</t>
+          <t>188,156</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>19,810</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>146,135</t>
+          <t>2,230,264</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3,428</t>
+          <t>44,355</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>187,395</t>
+          <t>186,855</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19,860</t>
+          <t>23,400</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>하락70</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>420,400</t>
+          <t>1,247,215</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8,387</t>
+          <t>29,306</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>187,327</t>
+          <t>186,598</t>
         </is>
       </c>
     </row>
@@ -2089,143 +2089,143 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>114,100</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>113,955</t>
+          <t>580,909</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>13,006</t>
+          <t>65,612</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>185,853</t>
+          <t>184,062</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>208,250</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>상승5,750</t>
+          <t>상승3,000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>109,212</t>
+          <t>701,333</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>22,642</t>
+          <t>131,848</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>185,230</t>
+          <t>183,253</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>188,100</t>
+          <t>155,500</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>상승3,100</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>254,190</t>
+          <t>217,390</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>47,737</t>
+          <t>34,106</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>183,351</t>
+          <t>178,322</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>156,500</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>37,822</t>
+          <t>286,831</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5,948</t>
+          <t>58,615</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>179,469</t>
+          <t>177,892</t>
         </is>
       </c>
     </row>
@@ -2237,106 +2237,106 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>80,700</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>상승900</t>
+          <t>상승200</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>198,138</t>
+          <t>830,279</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>15,983</t>
+          <t>67,026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>173,336</t>
+          <t>171,832</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>154,800</t>
+          <t>227,500</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>하락3,100</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>226,704</t>
+          <t>91,329</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>35,296</t>
+          <t>20,809</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>172,379</t>
+          <t>170,625</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>229,000</t>
+          <t>152,400</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20,334</t>
+          <t>664,482</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4,664</t>
+          <t>102,305</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>171,750</t>
+          <t>169,706</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>742,000</t>
+          <t>735,000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>상승8,000</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>160,245</t>
+          <t>415,383</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>119,962</t>
+          <t>309,979</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>163,240</t>
+          <t>161,700</t>
         </is>
       </c>
     </row>
@@ -2385,180 +2385,180 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>60,700</t>
+          <t>59,700</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>59,320</t>
+          <t>284,675</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3,588</t>
+          <t>17,222</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>152,977</t>
+          <t>150,457</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88,700</t>
+          <t>78,200</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>상승2,400</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+3.17%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>63,341</t>
+          <t>1,053,948</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5,582</t>
+          <t>81,551</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>136,795</t>
+          <t>137,572</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>삼성에피스홀딩스</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>87,500</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13,736</t>
+          <t>205,366</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7,538</t>
+          <t>18,075</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>135,115</t>
+          <t>134,944</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>삼성에피스홀딩스</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>313,000</t>
+          <t>533,000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>상승8,500</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>103,741</t>
+          <t>49,618</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>31,737</t>
+          <t>26,681</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>134,802</t>
+          <t>132,627</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>75,150</t>
+          <t>304,000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>하락650</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>95,599</t>
+          <t>379,373</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7,197</t>
+          <t>116,151</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>132,206</t>
+          <t>130,926</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>112,400</t>
+          <t>112,300</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>하락900</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>61,817</t>
+          <t>299,511</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>6,955</t>
+          <t>33,804</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>126,543</t>
+          <t>126,430</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2607,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>180,600</t>
+          <t>175,900</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>하락14,100</t>
+          <t>하락18,800</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-9.66%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>58,604</t>
+          <t>387,700</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10,716</t>
+          <t>69,023</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>125,308</t>
+          <t>122,046</t>
         </is>
       </c>
     </row>
@@ -2644,180 +2644,180 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>159,300</t>
+          <t>156,100</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락3,400</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16,188</t>
+          <t>136,693</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2,576</t>
+          <t>21,491</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>123,263</t>
+          <t>120,787</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>한국금융지주</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>328,500</t>
+          <t>216,000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>79,815</t>
+          <t>189,257</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>26,200</t>
+          <t>41,017</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>122,984</t>
+          <t>120,368</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>221,000</t>
+          <t>33,250</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락1,050</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-3.06%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40,940</t>
+          <t>750,858</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>8,934</t>
+          <t>25,240</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>123,154</t>
+          <t>118,484</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>34,100</t>
+          <t>24,500</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>158,041</t>
+          <t>582,098</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5,372</t>
+          <t>14,244</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>121,513</t>
+          <t>116,876</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24,600</t>
+          <t>310,000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>하락18,500</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>117,425</t>
+          <t>406,921</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2,874</t>
+          <t>129,276</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>117,353</t>
+          <t>116,058</t>
         </is>
       </c>
     </row>
@@ -2829,32 +2829,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>244,500</t>
+          <t>241,500</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29,428</t>
+          <t>127,397</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>7,186</t>
+          <t>31,197</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>115,908</t>
+          <t>114,486</t>
         </is>
       </c>
     </row>
@@ -2866,32 +2866,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>432,500</t>
+          <t>418,500</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락13,500</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-3.12%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17,609</t>
+          <t>62,038</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7,528</t>
+          <t>26,224</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>113,366</t>
+          <t>109,696</t>
         </is>
       </c>
     </row>
@@ -2903,32 +2903,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>399,500</t>
+          <t>387,500</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락18,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17,863</t>
+          <t>60,473</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>7,129</t>
+          <t>23,825</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>109,559</t>
+          <t>106,268</t>
         </is>
       </c>
     </row>
@@ -2940,32 +2940,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25,150</t>
+          <t>24,950</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>282,138</t>
+          <t>1,190,173</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7,083</t>
+          <t>29,838</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>92,607</t>
+          <t>91,871</t>
         </is>
       </c>
     </row>
@@ -2977,106 +2977,106 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1,221,000</t>
+          <t>1,188,000</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>하락28,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9,014</t>
+          <t>36,089</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11,024</t>
+          <t>43,554</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>91,978</t>
+          <t>89,492</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>120,600</t>
+          <t>277,000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>상승3,900</t>
+          <t>하락6,500</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>57,468</t>
+          <t>147,333</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6,835</t>
+          <t>41,524</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>90,400</t>
+          <t>86,424</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락5,300</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.41%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>36,725</t>
+          <t>700,012</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10,521</t>
+          <t>82,114</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>89,232</t>
+          <t>84,421</t>
         </is>
       </c>
     </row>
@@ -3088,106 +3088,106 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>97,800</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락3,300</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>46,290</t>
+          <t>283,903</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>27,210</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>87,335</t>
+          <t>84,388</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>118,800</t>
+          <t>111,100</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락5,600</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-4.80%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>263,292</t>
+          <t>379,203</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>31,181</t>
+          <t>43,477</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>87,210</t>
+          <t>83,279</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>123,500</t>
+          <t>178,900</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>하락3,200</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>23,923</t>
+          <t>61,367</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2,951</t>
+          <t>11,014</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>82,451</t>
+          <t>80,203</t>
         </is>
       </c>
     </row>
@@ -3199,69 +3199,69 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>138,200</t>
+          <t>136,000</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>상승1,400</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>23,207</t>
+          <t>122,626</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3,184</t>
+          <t>16,828</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>80,837</t>
+          <t>79,550</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>179,800</t>
+          <t>118,300</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락8,400</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-6.63%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11,912</t>
+          <t>107,159</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2,155</t>
+          <t>12,938</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>80,607</t>
+          <t>78,980</t>
         </is>
       </c>
     </row>
@@ -3273,143 +3273,143 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>100,200</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>상승1,300</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>70,128</t>
+          <t>194,867</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>7,045</t>
+          <t>19,448</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>79,807</t>
+          <t>78,851</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>44,700</t>
+          <t>94,700</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>824,115</t>
+          <t>214,470</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>37,415</t>
+          <t>20,550</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>76,836</t>
+          <t>74,163</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>96,800</t>
+          <t>303,000</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>50,565</t>
+          <t>204,500</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4,939</t>
+          <t>63,326</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>75,807</t>
+          <t>71,711</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한국타이어앤테크놀로지</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>310,000</t>
+          <t>57,400</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>71,032</t>
+          <t>306,690</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>22,399</t>
+          <t>17,655</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>73,368</t>
+          <t>71,104</t>
         </is>
       </c>
     </row>
@@ -3421,32 +3421,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>53,600</t>
+          <t>52,500</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>108,125</t>
+          <t>399,753</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>5,796</t>
+          <t>21,144</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>72,480</t>
+          <t>70,993</t>
         </is>
       </c>
     </row>
@@ -3458,254 +3458,254 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>561,000</t>
+          <t>551,000</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>상승20,000</t>
+          <t>상승10,000</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>24,437</t>
+          <t>104,774</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>13,428</t>
+          <t>58,430</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>71,870</t>
+          <t>70,589</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국타이어앤테크놀로지</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>57,800</t>
+          <t>15,950</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>55,110</t>
+          <t>955,437</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>3,193</t>
+          <t>15,248</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>71,600</t>
+          <t>68,558</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15,940</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>상승340</t>
+          <t>하락510</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>141,704</t>
+          <t>18,195,757</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2,232</t>
+          <t>292,545</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>68,515</t>
+          <t>66,084</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16,370</t>
+          <t>32,900</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>하락40</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6,891,115</t>
+          <t>2,474,239</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>110,431</t>
+          <t>82,143</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>68,037</t>
+          <t>64,484</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>32,750</t>
+          <t>36,800</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>하락950</t>
+          <t>하락8,200</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-18.22%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>666,790</t>
+          <t>10,597,245</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>21,977</t>
+          <t>409,911</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>64,190</t>
+          <t>63,256</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>68,900</t>
+          <t>54,500</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>36,044</t>
+          <t>129,972</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2,497</t>
+          <t>7,115</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>64,019</t>
+          <t>63,143</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>55,100</t>
+          <t>67,800</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락2,400</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>30,694</t>
+          <t>215,310</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>14,756</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>63,838</t>
+          <t>62,997</t>
         </is>
       </c>
     </row>
@@ -3717,180 +3717,180 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>166,000</t>
+          <t>163,900</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>하락2,800</t>
+          <t>하락4,900</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>37,665</t>
+          <t>145,464</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>6,278</t>
+          <t>23,983</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>63,445</t>
+          <t>62,643</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>211,000</t>
+          <t>61,200</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13,709</t>
+          <t>370,512</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2,879</t>
+          <t>22,884</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>61,563</t>
+          <t>59,294</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>62,100</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>103,027</t>
+          <t>67,308</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>6,412</t>
+          <t>13,922</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>60,166</t>
+          <t>59,229</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>두산밥캣</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>61,600</t>
+          <t>144,500</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>48,705</t>
+          <t>1,039,855</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2,999</t>
+          <t>150,927</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>59,047</t>
+          <t>58,265</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>두산밥캣</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>146,200</t>
+          <t>60,500</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>상승900</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>372,291</t>
+          <t>232,821</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>53,794</t>
+          <t>14,221</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>58,950</t>
+          <t>57,993</t>
         </is>
       </c>
     </row>
@@ -3902,32 +3902,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>11,690</t>
+          <t>11,530</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>하락60</t>
+          <t>하락220</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>671,151</t>
+          <t>2,781,164</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>7,841</t>
+          <t>32,401</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>58,450</t>
+          <t>57,650</t>
         </is>
       </c>
     </row>
@@ -3939,32 +3939,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18,670</t>
+          <t>18,430</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>상승220</t>
+          <t>하락20</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>95,239</t>
+          <t>567,429</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1,767</t>
+          <t>10,518</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>57,938</t>
+          <t>57,193</t>
         </is>
       </c>
     </row>
@@ -3976,32 +3976,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30,350</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>상승700</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>+2.36%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>51,890</t>
+          <t>281,164</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1,548</t>
+          <t>8,469</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>57,135</t>
+          <t>56,476</t>
         </is>
       </c>
     </row>
@@ -4013,32 +4013,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>87,200</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락3,400</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>29,866</t>
+          <t>128,695</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2,610</t>
+          <t>11,112</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>56,523</t>
+          <t>55,356</t>
         </is>
       </c>
     </row>
@@ -4050,81 +4050,81 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-4.29%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>621,375</t>
+          <t>1,768,774</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>18,805</t>
+          <t>52,432</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>55,561</t>
+          <t>54,070</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>174,200</t>
+          <t>132,200</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>상승8,400</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>+5.07%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>326,975</t>
+          <t>137,116</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>57,262</t>
+          <t>18,187</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>53,210</t>
+          <t>52,267</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>133,300</t>
+          <t>73,300</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4134,59 +4134,59 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19,696</t>
+          <t>173,624</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2,617</t>
+          <t>12,751</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>52,702</t>
+          <t>51,873</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>73,400</t>
+          <t>168,600</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+1.69%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>36,222</t>
+          <t>578,365</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2,666</t>
+          <t>100,051</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>51,943</t>
+          <t>51,499</t>
         </is>
       </c>
     </row>
@@ -4198,32 +4198,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>71,600</t>
+          <t>69,900</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>상승1,200</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>635,678</t>
+          <t>1,910,504</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>45,230</t>
+          <t>136,348</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>50,520</t>
+          <t>49,321</t>
         </is>
       </c>
     </row>
@@ -4235,69 +4235,69 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>225,500</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>23,435</t>
+          <t>94,990</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>5,341</t>
+          <t>21,496</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>48,474</t>
+          <t>48,582</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>포스코DX</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31,350</t>
+          <t>525,000</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>하락150</t>
+          <t>하락8,000</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>50,233</t>
+          <t>20,538</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1,581</t>
+          <t>10,716</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>47,663</t>
+          <t>46,654</t>
         </is>
       </c>
     </row>
@@ -4309,76 +4309,76 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>34,950</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락750</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>111,086</t>
+          <t>520,560</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>3,943</t>
+          <t>18,398</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>47,507</t>
+          <t>46,639</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>525,000</t>
+          <t>30,350</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>하락8,000</t>
+          <t>하락1,150</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2,783</t>
+          <t>337,809</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>46,654</t>
+          <t>46,143</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4388,101 +4388,101 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>상승2,750</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>+5.64%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>552,879</t>
+          <t>178,988</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>28,739</t>
+          <t>9,303</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>42,975</t>
+          <t>42,210</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>52,100</t>
+          <t>4,730</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>상승700</t>
+          <t>하락240</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>54,582</t>
+          <t>5,475,520</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2,863</t>
+          <t>26,438</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>42,701</t>
+          <t>41,081</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4,875</t>
+          <t>49,200</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>하락95</t>
+          <t>상승450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1,786,670</t>
+          <t>954,574</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>8,733</t>
+          <t>48,752</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>42,341</t>
+          <t>41,056</t>
         </is>
       </c>
     </row>
@@ -4494,32 +4494,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3,952</t>
+          <t>3,895</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>하락103</t>
+          <t>하락160</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-3.95%</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2,090,987</t>
+          <t>5,311,346</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>8,299</t>
+          <t>20,896</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>40,558</t>
+          <t>39,973</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18,140</t>
+          <t>18,240</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>98,151</t>
+          <t>743,013</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1,780</t>
+          <t>13,556</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>38,809</t>
+          <t>39,023</t>
         </is>
       </c>
     </row>
@@ -4568,32 +4568,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>100,900</t>
+          <t>98,100</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>하락1,200</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-3.92%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>25,492</t>
+          <t>121,810</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2,574</t>
+          <t>12,133</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>38,209</t>
+          <t>37,149</t>
         </is>
       </c>
     </row>
@@ -4605,32 +4605,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>244,500</t>
+          <t>242,000</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6,991</t>
+          <t>31,598</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1,704</t>
+          <t>7,669</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>37,415</t>
+          <t>37,032</t>
         </is>
       </c>
     </row>
@@ -4642,328 +4642,328 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>83,300</t>
+          <t>81,200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>하락600</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>9,501</t>
+          <t>42,975</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>3,514</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>36,911</t>
+          <t>35,981</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>189,500</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>상승6,700</t>
+          <t>상승700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>104,973</t>
+          <t>266,406</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>20,245</t>
+          <t>21,633</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>35,380</t>
+          <t>34,434</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>87,400</t>
+          <t>183,300</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>상승500</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>19,847</t>
+          <t>225,854</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>42,629</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>34,167</t>
+          <t>34,223</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>79,900</t>
+          <t>86,700</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>35,395</t>
+          <t>143,806</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2,825</t>
+          <t>12,542</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>34,178</t>
+          <t>33,893</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>43,400</t>
+          <t>64,400</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>상승6,500</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+11.23%</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>17,599</t>
+          <t>1,379,671</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>87,809</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>34,041</t>
+          <t>33,643</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>128,700</t>
+          <t>42,650</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락150</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8,872</t>
+          <t>71,924</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1,147</t>
+          <t>3,089</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>33,503</t>
+          <t>33,452</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>금호석유화학</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>64,300</t>
+          <t>128,000</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>상승6,400</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+11.05%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>473,849</t>
+          <t>72,585</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>29,223</t>
+          <t>9,327</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>33,591</t>
+          <t>33,321</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>36,050</t>
+          <t>87,500</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>30,325</t>
+          <t>46,831</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1,092</t>
+          <t>4,098</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>33,279</t>
+          <t>33,249</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>87,300</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>상승400</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>7,870</t>
+          <t>148,566</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>5,334</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>33,173</t>
+          <t>33,233</t>
         </is>
       </c>
     </row>
@@ -4975,180 +4975,180 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>218,500</t>
+          <t>216,500</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6,299</t>
+          <t>30,228</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1,370</t>
+          <t>6,573</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>32,893</t>
+          <t>32,592</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>114,100</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>상승6,500</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>+2.30%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>12,595</t>
+          <t>173,470</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>3,622</t>
+          <t>19,923</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>32,860</t>
+          <t>32,277</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>롯데지주</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>115,100</t>
+          <t>30,750</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>상승3,800</t>
+          <t>하락350</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>32,809</t>
+          <t>270,545</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>3,743</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>32,560</t>
+          <t>32,260</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>282,500</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3,641</t>
+          <t>40,522</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1,215</t>
+          <t>11,558</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>32,311</t>
+          <t>32,121</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>롯데지주</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>30,600</t>
+          <t>332,500</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락4,500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>53,684</t>
+          <t>25,214</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1,645</t>
+          <t>8,369</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>32,102</t>
+          <t>32,070</t>
         </is>
       </c>
     </row>
@@ -5160,180 +5160,180 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>223,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>상승2,500</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2,903</t>
+          <t>10,951</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>2,424</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>30,103</t>
+          <t>29,563</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>94,300</t>
+          <t>31,150</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>상승3,300</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>136,913</t>
+          <t>446,393</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>12,901</t>
+          <t>13,951</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>28,496</t>
+          <t>27,848</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>에스엘</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>60,100</t>
+          <t>91,700</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>하락900</t>
+          <t>상승700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>18,553</t>
+          <t>318,994</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1,109</t>
+          <t>29,854</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>27,916</t>
+          <t>27,711</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>에스엘</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>59,200</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>하락1,150</t>
+          <t>하락1,800</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>138,671</t>
+          <t>126,309</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>4,344</t>
+          <t>7,476</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>27,714</t>
+          <t>27,498</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>81,600</t>
+          <t>16,980</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>상승4,100</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>+5.29%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>316,323</t>
+          <t>486,688</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>26,001</t>
+          <t>8,340</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>27,680</t>
+          <t>27,274</t>
         </is>
       </c>
     </row>
@@ -5345,402 +5345,402 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>61,300</t>
+          <t>60,600</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락2,200</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>53,528</t>
+          <t>182,018</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3,298</t>
+          <t>11,128</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>27,585</t>
+          <t>27,270</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>동서</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>17,060</t>
+          <t>27,250</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>상승80</t>
+          <t>상승50</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>46,024</t>
+          <t>68,353</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>1,854</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>27,403</t>
+          <t>27,168</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>동서</t>
+          <t>이마트</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>27,100</t>
+          <t>97,800</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14,737</t>
+          <t>142,619</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>13,927</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>27,019</t>
+          <t>26,989</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>이마트</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>97,900</t>
+          <t>78,800</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>상승1,300</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>42,547</t>
+          <t>509,127</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>4,151</t>
+          <t>41,416</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>27,016</t>
+          <t>26,730</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>풍산</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>96,300</t>
+          <t>4,980</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>하락1,900</t>
+          <t>하락100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>56,726</t>
+          <t>3,051,959</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>5,481</t>
+          <t>15,210</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>26,987</t>
+          <t>26,622</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>풍산</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5,010</t>
+          <t>93,500</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>하락70</t>
+          <t>하락4,700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>441,213</t>
+          <t>214,655</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2,225</t>
+          <t>20,428</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>26,782</t>
+          <t>26,203</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>씨에스윈드</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>38,400</t>
+          <t>62,100</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>상승700</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>25,913</t>
+          <t>585,732</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>37,036</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>26,262</t>
+          <t>26,188</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>씨에스윈드</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>62,200</t>
+          <t>37,950</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>하락1,100</t>
+          <t>상승250</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>206,955</t>
+          <t>111,711</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>13,093</t>
+          <t>4,242</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>26,231</t>
+          <t>25,955</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>한국앤컴퍼니</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>66,900</t>
+          <t>27,100</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>하락2,400</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>670,096</t>
+          <t>86,413</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>45,107</t>
+          <t>2,324</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>25,886</t>
+          <t>25,727</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>71,200</t>
+          <t>66,400</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>90,204</t>
+          <t>1,574,485</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>6,404</t>
+          <t>104,826</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>25,534</t>
+          <t>25,693</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국앤컴퍼니</t>
+          <t>세아베스틸지주</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>26,750</t>
+          <t>70,200</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>하락850</t>
+          <t>하락2,300</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>18,430</t>
+          <t>226,183</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>15,984</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>25,395</t>
+          <t>25,175</t>
         </is>
       </c>
     </row>
@@ -5752,32 +5752,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>110,600</t>
+          <t>108,000</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락4,100</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>5,106</t>
+          <t>68,267</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>7,400</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>25,230</t>
+          <t>24,637</t>
         </is>
       </c>
     </row>
@@ -5789,143 +5789,143 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>51,900</t>
+          <t>51,500</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락900</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>43,153</t>
+          <t>173,130</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2,241</t>
+          <t>8,925</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>24,371</t>
+          <t>24,183</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>61,600</t>
+          <t>41,250</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>하락1,200</t>
+          <t>상승2,050</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+5.23%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>15,123</t>
+          <t>413,850</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>16,741</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>23,597</t>
+          <t>24,136</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>20,100</t>
+          <t>62,300</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>58,088</t>
+          <t>64,343</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1,165</t>
+          <t>3,981</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>23,123</t>
+          <t>23,865</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>39,300</t>
+          <t>19,830</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락220</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>42,802</t>
+          <t>533,111</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1,679</t>
+          <t>10,597</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>22,995</t>
+          <t>22,813</t>
         </is>
       </c>
     </row>
@@ -5937,32 +5937,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>375,500</t>
+          <t>373,500</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락5,000</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4,064</t>
+          <t>18,997</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1,523</t>
+          <t>7,113</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>22,840</t>
+          <t>22,719</t>
         </is>
       </c>
     </row>
@@ -5974,291 +5974,291 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>26,550</t>
+          <t>26,250</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>하락850</t>
+          <t>하락1,150</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-3.10%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>658,621</t>
+          <t>1,740,461</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>17,508</t>
+          <t>46,047</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>22,722</t>
+          <t>22,465</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>코오롱인더</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>81,600</t>
+          <t>42,800</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>상승2,800</t>
+          <t>상승950</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>+3.55%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>127,372</t>
+          <t>1,055,624</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>10,266</t>
+          <t>45,798</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>22,456</t>
+          <t>22,217</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>현대위아</t>
+          <t>코오롱인더</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>82,300</t>
+          <t>80,500</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>상승1,700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>16,967</t>
+          <t>637,640</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1,393</t>
+          <t>52,302</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>22,382</t>
+          <t>22,153</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>현대위아</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>43,100</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>상승1,250</t>
+          <t>하락1,600</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>+2.99%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>602,193</t>
+          <t>98,141</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>26,392</t>
+          <t>7,995</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>22,373</t>
+          <t>22,028</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>193,900</t>
+          <t>125,100</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>하락2,400</t>
+          <t>상승2,200</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>8,575</t>
+          <t>33,673</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1,672</t>
+          <t>4,176</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>22,007</t>
+          <t>21,622</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>아모레퍼시픽홀딩스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>28,050</t>
+          <t>188,800</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>22,647</t>
+          <t>50,332</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>9,623</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>21,447</t>
+          <t>21,428</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>아모레퍼시픽홀딩스</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>40,250</t>
+          <t>27,850</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>하락1,950</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-4.62%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>35,811</t>
+          <t>102,100</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1,446</t>
+          <t>2,871</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>21,369</t>
+          <t>21,294</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>미스토홀딩스</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>123,000</t>
+          <t>40,100</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락2,100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>6,458</t>
+          <t>160,204</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>6,428</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>21,259</t>
+          <t>21,290</t>
         </is>
       </c>
     </row>
@@ -6270,32 +6270,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>84,300</t>
+          <t>84,500</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락2,300</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>14,643</t>
+          <t>77,192</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1,245</t>
+          <t>6,513</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>19,076</t>
+          <t>19,121</t>
         </is>
       </c>
     </row>
@@ -6307,32 +6307,32 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>163,800</t>
+          <t>161,400</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>상승4,400</t>
+          <t>상승2,000</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>8,594</t>
+          <t>27,911</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1,395</t>
+          <t>4,526</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>18,979</t>
+          <t>18,701</t>
         </is>
       </c>
     </row>
@@ -6344,217 +6344,217 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>78,800</t>
+          <t>77,400</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락2,200</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>39,592</t>
+          <t>162,266</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3,107</t>
+          <t>12,620</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>18,601</t>
+          <t>18,270</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SK아이이테크놀로지</t>
+          <t>동원산업</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>21,650</t>
+          <t>39,950</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>하락450</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>29,735</t>
+          <t>33,344</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>1,329</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>17,707</t>
+          <t>17,637</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>동원산업</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>6,100</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>310,527</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>1,893</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>17,659</t>
+          <t>17,523</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>150,600</t>
+          <t>20,950</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>상승1,600</t>
+          <t>상승350</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>8,546</t>
+          <t>160,037</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1,282</t>
+          <t>3,358</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>17,600</t>
+          <t>17,516</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>148,300</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>하락120</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>80,484</t>
+          <t>33,879</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>5,063</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>17,523</t>
+          <t>17,331</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>SK아이이테크놀로지</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>20,800</t>
+          <t>21,050</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>상승200</t>
+          <t>하락1,050</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>21,810</t>
+          <t>162,509</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>3,467</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>17,390</t>
+          <t>17,216</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6566,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>394,500</t>
+          <t>389,500</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>상승9,500</t>
+          <t>상승4,500</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>+2.47%</t>
+          <t>+1.17%</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>10,317</t>
+          <t>35,949</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4,073</t>
+          <t>14,173</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>17,073</t>
+          <t>16,856</t>
         </is>
       </c>
     </row>
@@ -6603,106 +6603,106 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>42,200</t>
+          <t>41,950</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락750</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>43,559</t>
+          <t>162,594</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1,835</t>
+          <t>6,816</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>16,563</t>
+          <t>16,465</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>오리온홀딩스</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>17,420</t>
+          <t>25,450</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>상승450</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>180,676</t>
+          <t>321,854</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>3,121</t>
+          <t>8,142</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>16,136</t>
+          <t>15,943</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>오리온홀딩스</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>16,990</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>상승20</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>24,377</t>
+          <t>547,299</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>9,433</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>15,599</t>
+          <t>15,738</t>
         </is>
       </c>
     </row>
@@ -6714,32 +6714,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>366,000</t>
+          <t>362,500</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>하락4,500</t>
+          <t>하락8,000</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1,115</t>
+          <t>4,849</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>1,765</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>14,669</t>
+          <t>14,528</t>
         </is>
       </c>
     </row>
@@ -6751,32 +6751,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>25,150</t>
+          <t>24,450</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>상승850</t>
+          <t>상승150</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>+3.50%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>33,086</t>
+          <t>100,049</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>2,484</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>14,623</t>
+          <t>14,216</t>
         </is>
       </c>
     </row>
@@ -6788,32 +6788,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>51,800</t>
+          <t>51,600</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>상승1,200</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>+2.37%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>15,050</t>
+          <t>78,156</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>4,043</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>13,364</t>
+          <t>13,313</t>
         </is>
       </c>
     </row>
@@ -6825,106 +6825,106 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1,196,000</t>
+          <t>1,179,000</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>하락15,000</t>
+          <t>하락32,000</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1,964</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2,332</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>13,316</t>
+          <t>13,127</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>60,900</t>
+          <t>91,700</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>상승2,700</t>
+          <t>상승1,900</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>57,129</t>
+          <t>49,239</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3,443</t>
+          <t>4,560</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>12,762</t>
+          <t>12,657</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>91,600</t>
+          <t>59,400</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>상승1,800</t>
+          <t>상승1,200</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>+2.00%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>11,799</t>
+          <t>137,636</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1,080</t>
+          <t>8,243</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>12,643</t>
+          <t>12,448</t>
         </is>
       </c>
     </row>
@@ -6936,32 +6936,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16,800</t>
+          <t>16,590</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>하락210</t>
+          <t>하락420</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>19,445</t>
+          <t>99,974</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>1,666</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>12,356</t>
+          <t>12,201</t>
         </is>
       </c>
     </row>
@@ -6973,32 +6973,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>16,570</t>
+          <t>16,540</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>하락90</t>
+          <t>하락120</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>46,148</t>
+          <t>118,977</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1,969</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>11,621</t>
+          <t>11,600</t>
         </is>
       </c>
     </row>
@@ -7010,32 +7010,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>61,800</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>하락1,000</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>12,347</t>
+          <t>45,807</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>2,819</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>11,172</t>
+          <t>11,009</t>
         </is>
       </c>
     </row>
@@ -7047,32 +7047,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>118,600</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2,880</t>
+          <t>20,264</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>2,385</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>11,005</t>
+          <t>10,856</t>
         </is>
       </c>
     </row>
@@ -7099,12 +7099,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>3,714</t>
+          <t>30,425</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>1,525</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7116,49 +7116,49 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>지역난방공사</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>91,500</t>
+          <t>114,100</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>10,967</t>
+          <t>21,579</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,460</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>10,595</t>
+          <t>10,617</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>지역난방공사</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>113,800</t>
+          <t>90,200</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7168,22 +7168,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>3,377</t>
+          <t>54,770</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>4,960</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>10,589</t>
+          <t>10,444</t>
         </is>
       </c>
     </row>
@@ -7195,32 +7195,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>43,400</t>
+          <t>42,800</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>3,766</t>
+          <t>16,072</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>691</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>10,214</t>
+          <t>10,073</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>222,000</t>
+          <t>221,500</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1,916</t>
+          <t>10,577</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>2,362</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>9,945</t>
+          <t>9,923</t>
         </is>
       </c>
     </row>
@@ -7269,32 +7269,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>8,070</t>
+          <t>7,940</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>상승140</t>
+          <t>상승10</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>25,585</t>
+          <t>87,978</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>702</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>9,825</t>
+          <t>9,667</t>
         </is>
       </c>
     </row>
@@ -7306,32 +7306,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>55,800</t>
+          <t>54,300</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>8,237</t>
+          <t>45,828</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>2,525</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>9,653</t>
+          <t>9,393</t>
         </is>
       </c>
     </row>
@@ -7343,32 +7343,32 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>134,300</t>
+          <t>137,800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>상승2,100</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>6,092</t>
+          <t>69,677</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>9,635</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>8,730</t>
+          <t>8,957</t>
         </is>
       </c>
     </row>
@@ -7380,106 +7380,106 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>60,800</t>
+          <t>60,600</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>4,090</t>
+          <t>23,220</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1,404</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>8,427</t>
+          <t>8,399</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>세아제강지주</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7,480</t>
+          <t>192,000</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>상승140</t>
+          <t>상승5,200</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>+1.91%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>116,088</t>
+          <t>50,711</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>9,598</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>8,023</t>
+          <t>7,952</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>세아제강지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>185,600</t>
+          <t>7,210</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>하락1,200</t>
+          <t>하락130</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>14,137</t>
+          <t>365,214</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2,661</t>
+          <t>2,678</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>7,687</t>
+          <t>7,733</t>
         </is>
       </c>
     </row>
@@ -7491,32 +7491,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>26,400</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.75%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>12,231</t>
+          <t>31,671</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>834</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>7,654</t>
+          <t>7,668</t>
         </is>
       </c>
     </row>
@@ -7528,32 +7528,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>18,510</t>
+          <t>18,570</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>하락150</t>
+          <t>하락90</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>13,176</t>
+          <t>58,043</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1,075</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>7,567</t>
+          <t>7,591</t>
         </is>
       </c>
     </row>
@@ -7565,32 +7565,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>12,010</t>
+          <t>11,790</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>상승10</t>
+          <t>하락210</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>41,492</t>
+          <t>238,999</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>7,429</t>
+          <t>7,293</t>
         </is>
       </c>
     </row>
@@ -7602,32 +7602,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>20,950</t>
+          <t>20,600</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>29,127</t>
+          <t>127,838</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>2,656</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>7,259</t>
+          <t>7,137</t>
         </is>
       </c>
     </row>
@@ -7639,32 +7639,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>14,140</t>
+          <t>14,100</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>상승10</t>
+          <t>하락30</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>24,812</t>
+          <t>100,686</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1,426</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>6,650</t>
+          <t>6,631</t>
         </is>
       </c>
     </row>
@@ -7676,32 +7676,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>135,900</t>
+          <t>137,500</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>상승900</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1,429</t>
+          <t>2,677</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>365</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>6,455</t>
+          <t>6,531</t>
         </is>
       </c>
     </row>
@@ -7713,32 +7713,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>126,200</t>
+          <t>126,800</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>하락2,300</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1,935</t>
+          <t>2,876</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>361</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>6,310</t>
+          <t>6,340</t>
         </is>
       </c>
     </row>
@@ -7750,32 +7750,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>24,150</t>
+          <t>23,850</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>상승450</t>
+          <t>상승150</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>+1.90%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>24,294</t>
+          <t>91,050</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>2,180</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>5,989</t>
+          <t>5,915</t>
         </is>
       </c>
     </row>
@@ -7787,32 +7787,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>15,320</t>
+          <t>15,130</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>상승130</t>
+          <t>하락60</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>63,575</t>
+          <t>186,437</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>2,831</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>5,884</t>
+          <t>5,811</t>
         </is>
       </c>
     </row>
@@ -7824,32 +7824,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>273,500</t>
+          <t>278,500</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>하락5,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2,143</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>589</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>5,669</t>
+          <t>5,772</t>
         </is>
       </c>
     </row>
